--- a/media/Levels/kakeraMapLevel10.xlsx
+++ b/media/Levels/kakeraMapLevel10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C52E74-1D39-459D-A205-ABE984E24C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456196A3-6374-4804-BFDD-07EE7ED6DF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
+    <workbookView xWindow="2508" yWindow="0" windowWidth="15660" windowHeight="12168" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
   <sheets>
     <sheet name="Level_3" sheetId="1" r:id="rId1"/>
@@ -32948,28 +32948,28 @@
         <v>1</v>
       </c>
       <c r="CK71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS71">
         <v>0</v>
@@ -33400,28 +33400,28 @@
         <v>1</v>
       </c>
       <c r="CK72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS72">
         <v>0</v>
@@ -33852,28 +33852,28 @@
         <v>1</v>
       </c>
       <c r="CK73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS73">
         <v>0</v>
@@ -34304,28 +34304,28 @@
         <v>1</v>
       </c>
       <c r="CK74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS74">
         <v>0</v>
@@ -34756,28 +34756,28 @@
         <v>1</v>
       </c>
       <c r="CK75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS75">
         <v>0</v>
@@ -35208,28 +35208,28 @@
         <v>1</v>
       </c>
       <c r="CK76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS76">
         <v>0</v>
@@ -35660,28 +35660,28 @@
         <v>1</v>
       </c>
       <c r="CK77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS77">
         <v>0</v>
@@ -36112,28 +36112,28 @@
         <v>1</v>
       </c>
       <c r="CK78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CS78">
         <v>0</v>
